--- a/05-data-analysis/sample-files/purchase-history.xlsx
+++ b/05-data-analysis/sample-files/purchase-history.xlsx
@@ -25133,10 +25133,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -25231,12 +25231,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Approved By</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The final approver. From RM5,000 to RM50,000 this must be the Head of Procurement, after the HOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Received, Open or Cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rozita binti Mohd Ariff</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Head of Procurement (also the Procurement HOD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Hafiz bin Kamarudin</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Finance Director (also the Finance HOD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Salmah binti Idris</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Head of Department (HOD), Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tan Boon Hock</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Head of Department (HOD), IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Farah Nadiah binti Zulkifli</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Head of Department (HOD), Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Joanne Lee Pei Shan</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Head of Department (HOD), Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ganesh a/l Muniandy</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Head of Department (HOD), Warehouse</t>
         </is>
       </c>
     </row>
